--- a/data/감탄_데이터준비_샘플.xlsx
+++ b/data/감탄_데이터준비_샘플.xlsx
@@ -7097,7 +7097,7 @@
         </is>
       </c>
       <c r="B2" s="14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C2" s="14" t="inlineStr">
         <is>
@@ -7159,7 +7159,7 @@
         </is>
       </c>
       <c r="B3" s="14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C3" s="14" t="inlineStr">
         <is>
@@ -7234,7 +7234,7 @@
       </c>
       <c r="D4" s="14" t="inlineStr">
         <is>
-          <t>CNC, 가공기, 설비, 전기료</t>
+          <t>CNC,가공기;전기료</t>
         </is>
       </c>
       <c r="E4" s="14" t="inlineStr">
@@ -7300,7 +7300,7 @@
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>공조, 냉난방, 냉방, 전기료</t>
+          <t>냉난방,냉방;전기료</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
@@ -7366,7 +7366,7 @@
       </c>
       <c r="D6" s="14" t="inlineStr">
         <is>
-          <t>지게차, 경유</t>
+          <t>지게차;경유</t>
         </is>
       </c>
       <c r="E6" s="14" t="n"/>
@@ -7428,7 +7428,7 @@
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>납품차, 화물차, 차량, 경유, 주유</t>
+          <t>납품차,화물차,차량;경유,주유</t>
         </is>
       </c>
       <c r="E7" s="14" t="n"/>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>업무용 차량, 승용차, 휘발유, 주유</t>
+          <t>업무용 차량,승용차;휘발유,주유</t>
         </is>
       </c>
       <c r="E8" s="14" t="n"/>
@@ -7552,7 +7552,7 @@
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>구내 운반차, 운반차, 연료비</t>
+          <t>구내 운반차,운반차;연료비</t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
@@ -7618,7 +7618,7 @@
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>지게차, LPG, 충전</t>
+          <t>지게차;LPG</t>
         </is>
       </c>
       <c r="E10" s="14" t="n"/>
@@ -7812,7 +7812,7 @@
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
-          <t>보일러, 도시가스</t>
+          <t>도시가스</t>
         </is>
       </c>
       <c r="E13" s="14" t="n"/>
@@ -7940,7 +7940,7 @@
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>보일러, 등유</t>
+          <t>등유</t>
         </is>
       </c>
       <c r="E15" s="14" t="n"/>
@@ -8002,7 +8002,7 @@
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>열처리로, 연료</t>
+          <t>열처리로;연료</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
@@ -8068,7 +8068,7 @@
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>건조로, LPG</t>
+          <t>건조로;LPG</t>
         </is>
       </c>
       <c r="E17" s="14" t="n"/>
@@ -8130,7 +8130,7 @@
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>비상발전기, 발전기, 경유</t>
+          <t>비상발전기,발전기;경유</t>
         </is>
       </c>
       <c r="E18" s="14" t="n"/>
@@ -8514,7 +8514,7 @@
       </c>
       <c r="D24" s="14" t="inlineStr">
         <is>
-          <t>산소, 아르곤, 외</t>
+          <t>산소,아르곤;외</t>
         </is>
       </c>
       <c r="E24" s="14" t="inlineStr">
@@ -8770,7 +8770,7 @@
       </c>
       <c r="D28" s="14" t="inlineStr">
         <is>
-          <t>가스, 외 1종</t>
+          <t>가스;외 1종</t>
         </is>
       </c>
       <c r="E28" s="14" t="inlineStr">
@@ -8836,7 +8836,7 @@
       </c>
       <c r="D29" s="14" t="inlineStr">
         <is>
-          <t>경유, 외 1종</t>
+          <t>경유;외 1종</t>
         </is>
       </c>
       <c r="E29" s="14" t="inlineStr">
@@ -8902,7 +8902,7 @@
       </c>
       <c r="D30" s="14" t="inlineStr">
         <is>
-          <t>전기요금, 외</t>
+          <t>전기요금;외</t>
         </is>
       </c>
       <c r="E30" s="14" t="inlineStr">
@@ -9037,7 +9037,11 @@
           <t>고효율, 인버터, 공조설비, 설비구매</t>
         </is>
       </c>
-      <c r="E32" s="14" t="n"/>
+      <c r="E32" s="14" t="inlineStr">
+        <is>
+          <t>유지보수, 정기점검</t>
+        </is>
+      </c>
       <c r="F32" s="14" t="inlineStr">
         <is>
           <t>제외/참고</t>
@@ -9096,12 +9100,12 @@
       </c>
       <c r="D33" s="14" t="inlineStr">
         <is>
-          <t>CNC, 장비구매, 설비도입</t>
+          <t>CNC;장비구매,장비 구매,설비도입,설비 도입</t>
         </is>
       </c>
       <c r="E33" s="14" t="inlineStr">
         <is>
-          <t>전기료 아님</t>
+          <t>전기료 아님, 유지보수, 정기점검</t>
         </is>
       </c>
       <c r="F33" s="14" t="inlineStr">
@@ -9534,7 +9538,7 @@
       </c>
       <c r="D40" s="14" t="inlineStr">
         <is>
-          <t>폐기물, 폐수, 처리비</t>
+          <t>폐기물, 처리비</t>
         </is>
       </c>
       <c r="E40" s="14" t="n"/>
@@ -9662,7 +9666,7 @@
       </c>
       <c r="D42" s="14" t="inlineStr">
         <is>
-          <t>전기지게차, 충전전력</t>
+          <t>전기지게차;충전전력,충전 전력,충전</t>
         </is>
       </c>
       <c r="E42" s="14" t="n"/>
@@ -9790,7 +9794,7 @@
       </c>
       <c r="D44" s="14" t="inlineStr">
         <is>
-          <t>생산라인, 전력, kWh</t>
+          <t>생산라인;전력,kWh</t>
         </is>
       </c>
       <c r="E44" s="14" t="n"/>
@@ -9852,7 +9856,7 @@
       </c>
       <c r="D45" s="14" t="inlineStr">
         <is>
-          <t>컴프레서, 압축기, 전력</t>
+          <t>컴프레서,압축기;전력,전기료,전기요금</t>
         </is>
       </c>
       <c r="E45" s="14" t="inlineStr">
@@ -9918,7 +9922,7 @@
       </c>
       <c r="D46" s="14" t="inlineStr">
         <is>
-          <t>컴프레서, 수리비</t>
+          <t>컴프레서 수리, 압축기 수리, 수리비</t>
         </is>
       </c>
       <c r="E46" s="14" t="inlineStr">
@@ -9984,7 +9988,7 @@
       </c>
       <c r="D47" s="14" t="inlineStr">
         <is>
-          <t>최대수요, 피크, 전력요금</t>
+          <t>최대수요,피크;전력,전기료,전기요금</t>
         </is>
       </c>
       <c r="E47" s="14" t="n"/>
@@ -10309,7 +10313,11 @@
           <t>태양광, 태양광설비, 태양광패널</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>유지보수, 정기점검</t>
+        </is>
+      </c>
       <c r="F52" t="inlineStr">
         <is>
           <t>제외/참고</t>
@@ -10368,10 +10376,14 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ESS, 에너지저장장치, 배터리저장</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr"/>
+          <t>ESS, 에너지저장, 에너지 저장, 에너지저장장치, 배터리저장</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>유지보수, 정기점검</t>
+        </is>
+      </c>
       <c r="F53" t="inlineStr">
         <is>
           <t>제외/참고</t>
@@ -10430,12 +10442,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>전동지게차, 전동 지게차, 전기지게차 리스</t>
+          <t>전동지게차, 전동 지게차, 전기지게차 리스, 지게차 리스, 지게차 임대</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>전기지게차 충전전력(사용료) 아님</t>
+          <t>전기지게차 충전전력(사용료) 아님, 유지보수, 정기점검</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10496,10 +10508,14 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>히트펌프, 열펌프</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr"/>
+          <t>히트펌프, 히트 펌프, 열펌프</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>유지보수, 정기점검</t>
+        </is>
+      </c>
       <c r="F55" t="inlineStr">
         <is>
           <t>제외/참고</t>
@@ -10558,10 +10574,14 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>집진기, 대기방지시설</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr"/>
+          <t>집진기, 집진설비, 집진 설비, 집진시설, 대기방지시설, 대기오염방지시설, 대기오염방지설비, 대기오염방지</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>유지보수, 정기점검</t>
+        </is>
+      </c>
       <c r="F56" t="inlineStr">
         <is>
           <t>제외/참고</t>
@@ -10620,10 +10640,14 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>폐수처리설비, 수처리설비</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr"/>
+          <t>폐수처리설비, 폐수처리 설비, 폐수 처리설비, 폐수 처리 설비, 수처리설비, 수처리 설비</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>유지보수, 정기점검</t>
+        </is>
+      </c>
       <c r="F57" t="inlineStr">
         <is>
           <t>제외/참고</t>
@@ -10682,10 +10706,14 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>재활용설비, 재활용 설비</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr"/>
+          <t>재활용설비, 재활용 설비, 재활용시설, 재활용 시설</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>유지보수, 정기점검</t>
+        </is>
+      </c>
       <c r="F58" t="inlineStr">
         <is>
           <t>제외/참고</t>
@@ -18246,7 +18274,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>I042</t>
@@ -18284,7 +18311,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>I043</t>
@@ -18322,7 +18348,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>I044</t>
@@ -18402,7 +18427,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>I050</t>
@@ -18445,7 +18469,6 @@
           <t>탄소계산과 무관한 파일(전표 미생성)</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/감탄_데이터준비_샘플.xlsx
+++ b/data/감탄_데이터준비_샘플.xlsx
@@ -1,25 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-96" yWindow="0" windowWidth="11820" windowHeight="13056" tabRatio="412" firstSheet="0" activeTab="4" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="전표_샘플" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="분류_기준표_확장" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="배출계수" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="기대_결과" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="월별단가" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="company_master" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="mydata_documents" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="uploaded_files" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="k_taxonomy_mapping" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="facility_keywords" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="hitl_queue_mock" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="bank_loans_mock" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="portfolio_dashboard_mock" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="README_확장내역" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="전표_샘플" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분류_기준표_확장" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="배출계수" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="기대_결과" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="월별단가" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="company_master" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mydata_documents" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="uploaded_files" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="k_taxonomy_mapping" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="facility_keywords" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="hitl_queue_mock" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="bank_loans_mock" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="portfolio_dashboard_mock" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README_확장내역" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -7812,7 +7812,7 @@
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
-          <t>도시가스</t>
+          <t>보일러;도시가스</t>
         </is>
       </c>
       <c r="E13" s="14" t="n"/>
@@ -7940,7 +7940,7 @@
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>등유</t>
+          <t>보일러;등유</t>
         </is>
       </c>
       <c r="E15" s="14" t="n"/>

--- a/data/감탄_데이터준비_샘플.xlsx
+++ b/data/감탄_데이터준비_샘플.xlsx
@@ -8353,7 +8353,7 @@
         </is>
       </c>
       <c r="J21" s="14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" s="14" t="b">
         <v>0</v>
@@ -8365,7 +8365,7 @@
       </c>
       <c r="M21" s="14" t="inlineStr">
         <is>
-          <t>연료가 아니므로 Scope 1/2 산정 제외</t>
+          <t>순수 산소 충전은 연료 아님이 확실하나, 아르곤 등 혼합 공정가스 표현은 실제 연소 여부가 불명확해 사람검토 필요(정답지 I013 반영)</t>
         </is>
       </c>
       <c r="N21" s="14" t="inlineStr">
@@ -9253,7 +9253,7 @@
         </is>
       </c>
       <c r="J35" s="14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" s="14" t="b">
         <v>0</v>
@@ -9265,7 +9265,7 @@
       </c>
       <c r="M35" s="14" t="inlineStr">
         <is>
-          <t>MVP Scope1/2 제외</t>
+          <t>절삭공구 등 확실한 도구 구매는 제외이나, 절삭유·소모품처럼 유류성/모호한 품목이 섞여 매칭될 수 있어 사람검토 필요(정답지 I008·I025 반영)</t>
         </is>
       </c>
       <c r="N35" s="14" t="inlineStr">

--- a/data/감탄_데이터준비_샘플.xlsx
+++ b/data/감탄_데이터준비_샘플.xlsx
@@ -10836,7 +10836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H100"/>
+  <dimension ref="A1:H101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
   <cols>
     <col width="15.59765625" customWidth="1" style="22" min="1" max="1"/>
@@ -11082,31 +11082,47 @@
       </c>
     </row>
     <row r="7" ht="13.95" customHeight="1" s="22">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>가스종류 불명</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>등유</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>Scope 1</t>
         </is>
       </c>
-      <c r="C7" s="2" t="n"/>
-      <c r="D7" s="28" t="n"/>
-      <c r="E7" s="9" t="n"/>
-      <c r="F7" s="2" t="n"/>
-      <c r="G7" s="2" t="n"/>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>HITL 필요</t>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2.4914</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1332</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>원/L</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.gir.go.kr</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>에너지법 시행규칙 별표12 등유 순발열량 34.1 MJ/L와 국가 온실가스 인벤토리(GIR) CO2 배출계수 19.926 tC/TJ(=73,062 kgCO2/TJ, tC→CO2 44/12 환산)를 적용하여 환산. 단가는 오피넷 실내등유 전국 평균 판매가(2025-12 최신) 기준. 경유와 동일 산식으로 역산 검증(오차 0.6%) — 회계 담당 최종 검증 필요</t>
         </is>
       </c>
     </row>
     <row r="8" ht="13.95" customHeight="1" s="22">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>연료종류 불명</t>
+          <t>가스종류 불명</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -11128,30 +11144,48 @@
     <row r="9" ht="13.95" customHeight="1" s="22">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>없음</t>
+          <t>연료종류 불명</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>제외</t>
+          <t>Scope 1</t>
         </is>
       </c>
       <c r="C9" s="2" t="n"/>
-      <c r="D9" s="28" t="n">
-        <v>0</v>
-      </c>
+      <c r="D9" s="28" t="n"/>
       <c r="E9" s="9" t="n"/>
       <c r="F9" s="2" t="n"/>
       <c r="G9" s="2" t="n"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
+          <t>HITL 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="9" t="n"/>
+      <c r="F10" s="2" t="n"/>
+      <c r="G10" s="2" t="n"/>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>산정 제외</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="D10" s="10" t="n"/>
-      <c r="E10" s="10" t="n"/>
     </row>
     <row r="11">
       <c r="D11" s="10" t="n"/>
@@ -11512,6 +11546,10 @@
     <row r="100">
       <c r="D100" s="10" t="n"/>
       <c r="E100" s="10" t="n"/>
+    </row>
+    <row r="101">
+      <c r="D101" s="10" t="n"/>
+      <c r="E101" s="10" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>
